--- a/table/Supplementary Table 12.xlsx
+++ b/table/Supplementary Table 12.xlsx
@@ -379,7 +379,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Eligible under the prespecified rule</t>
+          <t>Eligible under the selection rule predefined for R6</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
